--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -733,49 +733,48 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
         </is>
       </c>
+      <c r="T4" s="3" t="n">
+        <v/>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -784,21 +783,25 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -820,123 +823,138 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7072
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12620
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">927
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v/>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
@@ -962,135 +980,137 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v/>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
@@ -1111,99 +1131,102 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v/>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1215,32 +1238,31 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
@@ -1266,125 +1288,133 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1411,128 +1441,126 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v/>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v/>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3822
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n">
@@ -1558,126 +1586,129 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1424
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v/>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1704,64 +1735,66 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>942</t>
         </is>
       </c>
       <c r="O11" s="3" t="n">
@@ -1775,55 +1808,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">3188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1850,123 +1883,131 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1122
+577
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">612
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1993,126 +2034,129 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2627
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v/>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2139,37 +2183,37 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2181,31 +2225,31 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9043
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2217,55 +2261,53 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1252
-</t>
-        </is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v/>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="n">
@@ -2291,36 +2333,37 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">983
+</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2332,85 +2375,90 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2437,42 +2485,42 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2481,82 +2529,82 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9532
-</t>
-        </is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v/>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18417
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -2583,119 +2631,132 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+</t>
+        </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8083
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2722,126 +2783,128 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2456
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4921
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2518
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">649
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v/>
-      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2868,127 +2931,132 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262622
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9812
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="n">
@@ -3014,129 +3082,128 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3163,129 +3230,133 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12922
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9272
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3312,133 +3383,130 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>381</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1842
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3465,131 +3533,131 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">3894
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5360
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4278
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n">
@@ -3615,124 +3683,125 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32828
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
@@ -3765,130 +3834,129 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1446
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4978
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0926
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3912
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22 1
 </t>
         </is>
       </c>
@@ -3915,19 +3983,18 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3939,106 +4006,107 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">632
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n">
@@ -4064,128 +4132,133 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2393
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="n">
@@ -4211,43 +4284,43 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4259,83 +4332,85 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19584
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8539
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n">
@@ -4361,13 +4436,13 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1539
 </t>
         </is>
       </c>
@@ -4379,114 +4454,115 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26511
+          <t xml:space="preserve">16825
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1902
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1042
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n">
@@ -4512,49 +4588,54 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">3061
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>588</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>896</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -4566,70 +4647,71 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">39086
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10426
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">3225
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4656,126 +4738,128 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">27511
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">4526
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">1397
+</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>226444</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4802,77 +4886,90 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2829
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4884,37 +4981,37 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4941,100 +5038,96 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139326
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -5046,25 +5139,25 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -5086,81 +5179,88 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9282
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5172,19 +5272,18 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
@@ -5196,25 +5295,25 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -5241,130 +5340,125 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9282
-</t>
-        </is>
+          <t xml:space="preserve">7922
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v/>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>801</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2218
-</t>
-        </is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v/>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -5386,59 +5480,64 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5447,12 +5546,15 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180902
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -5468,49 +5570,49 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">2973
+</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n">
@@ -5536,69 +5638,74 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>846344</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14418
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09502
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">94503
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -5608,54 +5715,56 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">12421
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">2672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">324
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n">
@@ -5681,65 +5790,62 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t xml:space="preserve">1615
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>883384</t>
-        </is>
+          <t xml:space="preserve">7857
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v/>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -5757,56 +5863,54 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n">
@@ -5832,48 +5936,47 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5883,12 +5986,14 @@
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="n">
-        <v/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5903,13 +6008,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5921,7 +6026,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5933,25 +6038,25 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5973,135 +6078,137 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2478
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1948
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1983
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">472
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -6123,54 +6230,57 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6180,39 +6290,45 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="3" t="n">
-        <v/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6224,25 +6340,25 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -6270,63 +6386,60 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v/>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6338,64 +6451,67 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19221
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
@@ -6423,45 +6539,42 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v/>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6479,41 +6592,55 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
       </c>
       <c r="O43" s="3" t="n">
         <v/>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">3
+6
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -6524,25 +6651,25 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9272
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Z43" s="3" t="n">
@@ -6568,47 +6695,51 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">4262
+7
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">2429
+14
+</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">7
+7
 </t>
         </is>
       </c>
@@ -6620,7 +6751,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13663
+          <t xml:space="preserve">77 777
 </t>
         </is>
       </c>
@@ -6629,25 +6760,24 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21213
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
@@ -6656,13 +6786,13 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6674,14 +6804,13 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">3272
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>504</t>
         </is>
       </c>
       <c r="Z44" s="3" t="n">
@@ -6707,7 +6836,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -6719,35 +6848,36 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>455</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">2828
 </t>
         </is>
       </c>
@@ -6763,14 +6893,15 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
-</t>
-        </is>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v/>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -6778,18 +6909,21 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n">
-        <v/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6810,7 +6944,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 2
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6835,8 +6969,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -6846,19 +6983,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -6867,13 +7004,13 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K46" s="3" t="n">
@@ -6884,66 +7021,67 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">8
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v/>
+      <c r="T46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12901
+</t>
+        </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501
-</t>
-        </is>
+          <t xml:space="preserve">1999
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v/>
       </c>
       <c r="Z46" s="3" t="n">
         <v/>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -694,7 +694,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -721,7 +721,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
@@ -733,47 +733,49 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">916
 </t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -783,27 +785,21 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v/>
       </c>
       <c r="Z4" s="3" t="n">
         <v/>
@@ -823,40 +819,36 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v/>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -880,90 +872,89 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -985,136 +976,135 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">0170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v/>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v/>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">2074
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2513
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1131,138 +1121,132 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v/>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">2105
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
-        </is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v/>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
@@ -1288,134 +1272,125 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v/>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
@@ -1441,125 +1416,126 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9578
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14546
+</t>
+        </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11109
+</t>
+        </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3186
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
+          <t xml:space="preserve">1269
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v/>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2311
 </t>
         </is>
       </c>
@@ -1586,13 +1562,13 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1604,116 +1580,113 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v/>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v/>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">912
+</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2162
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1735,66 +1708,63 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v/>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="O11" s="3" t="n">
@@ -1802,61 +1772,60 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3188
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -1883,131 +1852,125 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v/>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v/>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1945
 </t>
         </is>
       </c>
@@ -2034,129 +1997,122 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v/>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>938</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2627
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -2183,130 +2139,128 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1495
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>43414</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29234
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2824
-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2333,55 +2287,50 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">983
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v/>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2391,74 +2340,72 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+      <c r="N15" s="3" t="n">
+        <v/>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -2485,42 +2432,42 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -2529,82 +2476,82 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">11823
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">17088
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -2631,132 +2578,121 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">4129
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1466
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2783,128 +2719,124 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>466</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2456
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
+          <t xml:space="preserve">4110
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v/>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">2288
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v/>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4921
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2931,131 +2863,119 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">29505
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v/>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262622
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v/>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3082,128 +3002,120 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v/>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v/>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3230,133 +3142,126 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v/>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3383,130 +3288,130 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>381</t>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v/>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">2399
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">9562
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1399
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1947
 </t>
         </is>
       </c>
@@ -3533,131 +3438,123 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">11441
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2904
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v/>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v/>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3894
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">024644
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
+          <t xml:space="preserve">14209
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v/>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">9316
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">11210
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1072
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">93606
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">11084
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">09278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n">
@@ -3683,125 +3580,114 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">18298
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32828
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
+          <t>13164</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v/>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7282
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -3834,129 +3720,129 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4978
-</t>
-        </is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v/>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">11922
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1090
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0926
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 1
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3983,18 +3869,19 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1592
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4006,106 +3893,102 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">2188
+</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">7162
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4132,73 +4015,70 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v/>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4209,55 +4089,52 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v/>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1802
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4284,132 +4161,128 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v/>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1190809
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8539
+          <t xml:space="preserve">402
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">5622
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>537</t>
+          <t xml:space="preserve">538
+</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4436,13 +4309,13 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4454,67 +4327,64 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16825
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
+          <t xml:space="preserve">1958
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v/>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4526,25 +4396,25 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1394
 </t>
         </is>
       </c>
@@ -4556,13 +4426,14 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n">
@@ -4588,130 +4459,126 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3061
+          <t xml:space="preserve">194984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">2927
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39086
-</t>
-        </is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v/>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3222
-</t>
-        </is>
+          <t xml:space="preserve">11123
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v/>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1538222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10426
+          <t xml:space="preserve">11042
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3225
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">9284
 </t>
         </is>
       </c>
@@ -4738,128 +4605,122 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>806</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v/>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27511
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v/>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4526
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4886,134 +4747,127 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">14183
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v/>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12196
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2829
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v/>
       </c>
       <c r="Z32" s="3" t="n">
         <v/>
@@ -5038,73 +4892,74 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">945
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1879
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v/>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -5115,49 +4970,49 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">1803
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
@@ -5179,88 +5034,75 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v/>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v/>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12825
 </t>
         </is>
       </c>
@@ -5272,48 +5114,48 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5340,125 +5182,127 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">8320
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5480,139 +5324,133 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v/>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
         <v/>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+      <c r="N36" s="3" t="n">
+        <v/>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">12312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">3852
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n">
@@ -5638,132 +5476,129 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">11615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">87110
+</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">9811
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94503
-</t>
-        </is>
+          <t xml:space="preserve">9410
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v/>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">9506
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">2413
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12421
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672
+          <t xml:space="preserve">3672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5790,121 +5625,119 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7857
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v/>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">269
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">12749
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5936,47 +5769,47 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">024516
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
@@ -5988,34 +5821,33 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -6026,37 +5858,36 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">19482
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -6078,137 +5909,134 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v/>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">018
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">2998
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">270
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -6230,135 +6058,129 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v/>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">2324
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">10856
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v/>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6391,133 +6213,125 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">11229
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">11020
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">544
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v/>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2662
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v/>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12221
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">9603
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">102712
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2167
 </t>
         </is>
       </c>
@@ -6542,135 +6356,71 @@
       <c r="C43" s="3" t="n">
         <v/>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v/>
       </c>
       <c r="O43" s="3" t="n">
         <v/>
       </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+      <c r="P43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v/>
       </c>
       <c r="Z43" s="3" t="n">
         <v/>
@@ -6693,55 +6443,29 @@
       <c r="C44" s="3" t="n">
         <v/>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v/>
       </c>
       <c r="L44" s="3" t="n">
         <v/>
@@ -6749,69 +6473,41 @@
       <c r="M44" s="3" t="n">
         <v/>
       </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
+      <c r="N44" s="3" t="n">
+        <v/>
       </c>
       <c r="O44" s="3" t="n">
         <v/>
       </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2418
-</t>
-        </is>
+      <c r="P44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v/>
       </c>
       <c r="T44" s="3" t="n">
         <v/>
       </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3272
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
+      <c r="U44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v/>
       </c>
       <c r="Z44" s="3" t="n">
         <v/>
@@ -6836,7 +6532,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
@@ -6848,108 +6544,112 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v/>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v/>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v/>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
         <v/>
@@ -6971,47 +6671,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v/>
       </c>
       <c r="H46" s="3" t="n">
         <v/>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
+      <c r="I46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v/>
       </c>
       <c r="K46" s="3" t="n">
         <v/>
@@ -7019,30 +6702,17 @@
       <c r="L46" s="3" t="n">
         <v/>
       </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
+      <c r="M46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v/>
       </c>
       <c r="Q46" s="3" t="n">
         <v/>
@@ -7050,38 +6720,35 @@
       <c r="R46" s="3" t="n">
         <v/>
       </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+      <c r="S46" s="3" t="n">
+        <v/>
       </c>
       <c r="T46" s="3" t="n">
         <v/>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12901
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
+      <c r="U46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v/>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">92110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198855
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165608
+</t>
+        </is>
       </c>
       <c r="Z46" s="3" t="n">
         <v/>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
@@ -706,7 +706,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -716,12 +716,15 @@
 </t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -733,19 +736,19 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -757,7 +760,8 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">306
+</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -768,13 +772,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t xml:space="preserve">452
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -824,13 +829,13 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -842,19 +847,19 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -872,13 +877,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">7146
 </t>
         </is>
       </c>
@@ -890,17 +895,19 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">994
+</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -912,7 +919,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -924,36 +931,38 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -976,25 +985,25 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -1004,8 +1013,11 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
-        <v/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1015,76 +1027,79 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2074
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
@@ -1102,7 +1117,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1126,7 +1141,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2105
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -1138,7 +1153,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1150,7 +1165,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -1174,25 +1189,29 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
         <v/>
       </c>
-      <c r="O7" s="3" t="n">
-        <v/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>013</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1209,21 +1228,18 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v/>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1255,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1249,8 +1265,11 @@
 </t>
         </is>
       </c>
-      <c r="Z7" s="3" t="n">
-        <v/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1278,13 +1297,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1302,18 +1321,20 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1333,13 +1354,14 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">080
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1350,7 +1372,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1362,7 +1384,8 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>662</t>
+          <t xml:space="preserve">662
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1373,7 +1396,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1385,16 +1408,21 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1422,43 +1450,43 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9578
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
@@ -1474,12 +1502,15 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="n">
-        <v/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1001
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14546
+          <t xml:space="preserve">4516
 </t>
         </is>
       </c>
@@ -1497,13 +1528,14 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11109
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1514,29 +1546,31 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n">
@@ -1568,24 +1602,27 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1595,7 +1632,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">08604
 </t>
         </is>
       </c>
@@ -1610,11 +1647,15 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -1624,8 +1665,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1648,13 +1688,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1666,25 +1706,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1714,40 +1754,44 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>483</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1758,17 +1802,21 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">1183
+</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -1778,54 +1826,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">2398
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1847,8 +1896,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -1858,7 +1910,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -1870,13 +1922,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -1888,80 +1940,88 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1612
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -1970,12 +2030,15 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1945
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -2003,51 +2066,61 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2059,19 +2132,20 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2088,7 +2162,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2106,18 +2180,21 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -2134,8 +2211,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 3 3 1
+</t>
+        </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -2151,13 +2231,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2181,56 +2261,61 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>43414</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -2242,7 +2327,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -2260,12 +2345,15 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9514
+</t>
+        </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -2287,19 +2375,20 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">28919
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2310,22 +2399,26 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2336,28 +2429,31 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2369,48 +2465,51 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -2450,12 +2549,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">481
+</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2467,16 +2567,20 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">9513
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2487,29 +2591,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t xml:space="preserve">94552
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11823
+          <t xml:space="preserve">11829
 </t>
         </is>
       </c>
@@ -2521,37 +2627,34 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">213142
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11585
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17088
-</t>
-        </is>
+          <t xml:space="preserve">112746
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v/>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1005
 </t>
         </is>
       </c>
@@ -2573,96 +2676,105 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2518
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">233
 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4129
-</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">649
@@ -2677,16 +2789,19 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">222 3
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="n">
-        <v/>
-      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2719,12 +2834,13 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">3089
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2742,18 +2858,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2765,13 +2882,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2780,22 +2897,26 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2806,31 +2927,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2863,7 +2984,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29505
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
@@ -2887,42 +3008,52 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14183
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
       </c>
       <c r="N19" s="3" t="n">
         <v/>
       </c>
-      <c r="O19" s="3" t="n">
-        <v/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2933,49 +3064,49 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2997,12 +3128,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2853
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3019,13 +3154,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>486</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3036,39 +3172,46 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
         <v/>
       </c>
-      <c r="O20" s="3" t="n">
-        <v/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3086,36 +3229,37 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3142,7 +3286,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3154,19 +3298,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3184,30 +3328,34 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="N21" s="3" t="n">
         <v/>
       </c>
-      <c r="O21" s="3" t="n">
-        <v/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3219,7 +3367,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3231,19 +3379,19 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3253,15 +3401,12 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
+      <c r="X21" s="3" t="n">
+        <v/>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3288,19 +3433,19 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3312,19 +3457,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3336,28 +3481,31 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3369,7 +3517,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3381,28 +3529,28 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562
+          <t xml:space="preserve">8562
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
@@ -3411,7 +3559,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
@@ -3433,38 +3581,47 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11441
+          <t xml:space="preserve">19446
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904
+          <t xml:space="preserve">9104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -3474,18 +3631,19 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024644
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">939
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3494,7 +3652,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316
+          <t xml:space="preserve">9312
 </t>
         </is>
       </c>
@@ -3506,7 +3664,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -3518,36 +3676,37 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93606
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09278
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3580,25 +3739,25 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18298
+          <t xml:space="preserve">8228
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1914
 </t>
         </is>
       </c>
@@ -3610,12 +3769,15 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10589
+</t>
+        </is>
       </c>
       <c r="K24" s="3" t="n">
         <v/>
@@ -3628,18 +3790,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t xml:space="preserve">2186
+</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
         <v/>
       </c>
-      <c r="O24" s="3" t="n">
-        <v/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 312
+</t>
+        </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3651,19 +3817,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3675,21 +3841,18 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2817
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
+      <c r="X24" s="3" t="n">
+        <v/>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
@@ -3726,7 +3889,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3744,13 +3907,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3762,37 +3925,37 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11922
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1090
-</t>
-        </is>
-      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -3801,7 +3964,8 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3812,37 +3976,37 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1692
+          <t xml:space="preserve">1678
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">591
 </t>
         </is>
       </c>
@@ -3869,13 +4033,13 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3899,7 +4063,8 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3910,31 +4075,37 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 18
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">7 91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3946,19 +4117,18 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3982,7 +4152,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -4010,8 +4180,11 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -4021,7 +4194,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -4039,7 +4212,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4057,7 +4230,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4069,16 +4242,20 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4095,7 +4272,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4107,34 +4284,34 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">632
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="U27" s="3" t="n">
-        <v/>
-      </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v/>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4161,13 +4338,13 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -4179,19 +4356,19 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4203,33 +4380,37 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>463</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190809
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -4241,13 +4422,14 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">2740
+</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4258,31 +4440,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5622
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4315,70 +4497,72 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1918
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1892
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1958
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4408,31 +4592,31 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4454,12 +4638,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194984
+          <t xml:space="preserve">19484
 </t>
         </is>
       </c>
@@ -4489,31 +4676,31 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2927
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4522,63 +4709,67 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">9207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11123
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538222
+          <t xml:space="preserve">33222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">10881
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11042
+          <t xml:space="preserve">11841
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9284
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -4605,13 +4796,13 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">2397
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4623,7 +4814,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4635,28 +4826,36 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
         <v/>
       </c>
-      <c r="L31" s="3" t="n">
-        <v/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
@@ -4666,61 +4865,61 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">773
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4747,30 +4946,32 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4781,7 +4982,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4803,12 +5004,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
-        <v/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12196
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4826,7 +5030,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4838,31 +5042,31 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">4155
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -4887,8 +5091,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -4898,19 +5105,19 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4922,37 +5129,43 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -4982,37 +5195,37 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -5034,12 +5247,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -5051,7 +5267,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5069,19 +5285,19 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -5091,24 +5307,33 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1511
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12825
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5126,13 +5351,14 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -5143,19 +5369,19 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5182,31 +5408,30 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5234,15 +5459,21 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9942
 </t>
         </is>
       </c>
@@ -5272,19 +5503,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8320
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -5296,13 +5527,13 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
@@ -5329,7 +5560,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
@@ -5353,19 +5584,19 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -5384,30 +5615,33 @@
       <c r="M36" s="3" t="n">
         <v/>
       </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5425,7 +5659,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5443,13 +5677,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5482,7 +5716,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -5494,47 +5728,51 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87110
+          <t xml:space="preserve">8180
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">0117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
@@ -5544,7 +5782,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -5556,34 +5794,34 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2413
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1299
@@ -5592,13 +5830,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3672
+          <t xml:space="preserve">36722
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">5372
 </t>
         </is>
       </c>
@@ -5625,7 +5863,8 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5636,7 +5875,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">25246
 </t>
         </is>
       </c>
@@ -5648,19 +5887,19 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5669,27 +5908,31 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5707,25 +5950,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12749
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5743,7 +5986,8 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n">
@@ -5769,59 +6013,61 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024516
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -5830,13 +6076,14 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -5847,7 +6094,8 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t xml:space="preserve">1426
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5858,13 +6106,14 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19482
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
@@ -5881,15 +6130,12 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v/>
       </c>
       <c r="Z39" s="3" t="n">
         <v/>
@@ -5914,69 +6160,73 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5118
+</t>
+        </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5988,31 +6238,31 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2608
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">1926
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6024,13 +6274,13 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">2518
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6063,19 +6313,19 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10856
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6087,37 +6337,37 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">2049
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6126,7 +6376,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -6138,25 +6388,25 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6174,13 +6424,13 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -6213,127 +6463,120 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11229
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">544
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19502
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v/>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12221
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9603
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102712
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2167
-</t>
-        </is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v/>
       </c>
       <c r="Z42" s="3" t="n">
         <v/>
@@ -6353,8 +6596,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D43" s="3" t="n">
         <v/>
@@ -6440,8 +6686,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="n">
         <v/>
@@ -6532,72 +6781,79 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6606,48 +6862,49 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">2412
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">5097
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8187
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9663
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">02712
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6669,84 +6926,129 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v/>
+      <c r="C46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
       </c>
       <c r="K46" s="3" t="n">
         <v/>
       </c>
-      <c r="L46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
       </c>
       <c r="Q46" s="3" t="n">
         <v/>
       </c>
-      <c r="R46" s="3" t="n">
-        <v/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
       </c>
       <c r="S46" s="3" t="n">
         <v/>
       </c>
-      <c r="T46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92110
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198855
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165608
+          <t xml:space="preserve">12111011
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -694,7 +694,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -706,7 +706,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -742,13 +742,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -772,14 +771,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
-</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -790,7 +788,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -824,8 +822,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -841,7 +842,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -853,25 +854,24 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -883,19 +883,19 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">994
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -919,7 +919,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -931,19 +931,19 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">2439
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -985,121 +985,121 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1210,13 +1210,13 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">4201
 </t>
         </is>
       </c>
@@ -1228,18 +1228,21 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1255,7 +1258,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1267,7 +1270,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1286,8 +1289,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -1303,7 +1309,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1321,13 +1327,13 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1384,7 +1390,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1396,7 +1402,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1414,13 +1420,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1450,7 +1456,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
@@ -1462,7 +1468,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
@@ -1480,28 +1486,28 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">9441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">926
 </t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1001
@@ -1510,8 +1516,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1534,7 +1539,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1546,13 +1551,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1570,7 +1575,8 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n">
@@ -1591,8 +1597,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1614,13 +1623,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1632,12 +1641,15 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08604
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1653,7 +1665,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1694,7 +1706,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1724,7 +1736,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1772,13 +1784,13 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -1790,14 +1802,13 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1808,15 +1819,12 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v/>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -1832,31 +1840,31 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2398
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1868,7 +1876,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1898,7 +1906,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1910,7 +1918,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1922,13 +1930,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
@@ -1964,7 +1972,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1982,7 +1990,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1994,19 +2002,19 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2018,7 +2026,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2030,13 +2038,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2072,7 +2080,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2084,7 +2092,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2096,7 +2104,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2120,7 +2128,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2138,7 +2146,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2162,7 +2170,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2211,11 +2219,8 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 3 3 1
-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v/>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2236,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2273,19 +2278,16 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v/>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -2297,7 +2299,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -2309,13 +2311,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -2327,7 +2329,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -2345,13 +2347,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">7172
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9514
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2370,18 +2372,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28919
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2405,19 +2410,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2429,25 +2434,25 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
@@ -2465,7 +2470,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -2489,7 +2494,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2507,7 +2512,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2531,19 +2536,18 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">19404
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2555,7 +2559,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -2567,13 +2571,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -2597,7 +2601,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94552
+          <t xml:space="preserve">4532
 </t>
         </is>
       </c>
@@ -2609,13 +2613,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11829
+          <t xml:space="preserve">11273
 </t>
         </is>
       </c>
@@ -2627,25 +2631,25 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213142
+          <t xml:space="preserve">0182
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11585
+          <t xml:space="preserve">9848
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112746
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1005
+          <t xml:space="preserve">100646
 </t>
         </is>
       </c>
@@ -2676,15 +2680,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v/>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2696,7 +2697,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2720,7 +2721,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -2735,15 +2736,12 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v/>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -2753,7 +2751,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2765,19 +2763,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -2789,7 +2787,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222 3
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2834,37 +2832,36 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2882,13 +2879,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2909,8 +2906,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2927,13 +2923,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2945,7 +2941,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2979,12 +2975,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -3008,7 +3007,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3031,7 +3030,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3070,19 +3069,19 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3128,21 +3127,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v/>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3190,12 +3186,15 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3223,25 +3222,25 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -3253,7 +3252,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3286,8 +3285,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3304,22 +3302,22 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3328,7 +3326,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -3361,13 +3359,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3379,13 +3377,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -3433,8 +3431,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3445,34 +3442,34 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2328
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -3487,13 +3484,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3529,7 +3526,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562
+          <t xml:space="preserve">89562
 </t>
         </is>
       </c>
@@ -3581,58 +3578,53 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v/>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19446
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3643,24 +3635,23 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9312
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v/>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -3670,7 +3661,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -3682,7 +3673,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">3602
 </t>
         </is>
       </c>
@@ -3700,19 +3691,19 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">0949278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3739,7 +3730,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3751,13 +3742,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3769,14 +3760,13 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10589
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
@@ -3784,7 +3774,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -3799,13 +3789,13 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 312
+          <t xml:space="preserve">5812
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3817,19 +3807,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">28239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -3841,7 +3831,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2817
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -3878,13 +3868,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3895,58 +3887,54 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v/>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3976,8 +3964,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -3988,25 +3975,25 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1678
+          <t xml:space="preserve">8713
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4033,7 +4020,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2986
 </t>
         </is>
       </c>
@@ -4057,7 +4044,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4075,37 +4062,34 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 18
-</t>
-        </is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 91
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4117,18 +4101,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -4180,11 +4165,8 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v/>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -4194,7 +4176,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -4212,7 +4194,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4224,13 +4206,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4242,19 +4224,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4266,13 +4248,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4290,13 +4272,13 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -4311,7 +4293,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4338,13 +4320,13 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4356,7 +4338,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4368,7 +4350,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4380,37 +4362,36 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">12724
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4428,7 +4409,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2740
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
@@ -4440,32 +4421,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n">
@@ -4509,7 +4489,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4521,7 +4501,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4545,19 +4525,16 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v/>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>407</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4580,7 +4557,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4604,7 +4581,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4616,7 +4593,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4638,27 +4615,24 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v/>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19484
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -4688,19 +4662,19 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
@@ -4709,25 +4683,24 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9207
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
@@ -4739,37 +4712,36 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10881
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11841
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -4796,19 +4768,19 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4841,7 +4813,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4853,7 +4825,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4865,7 +4837,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4877,7 +4849,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -4889,13 +4861,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">641
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -4919,7 +4891,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -4946,8 +4918,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4958,7 +4929,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4970,19 +4941,19 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4994,25 +4965,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
+      <c r="N32" s="3" t="n">
+        <v/>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -5030,7 +4998,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5042,13 +5010,13 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -5066,7 +5034,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5091,21 +5059,17 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
+      <c r="C33" s="3" t="n">
+        <v/>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5129,7 +5093,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5147,28 +5111,25 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -5183,7 +5144,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5195,7 +5156,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5207,13 +5168,13 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -5225,7 +5186,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5247,11 +5208,8 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v/>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5219,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5291,13 +5249,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5309,19 +5267,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5333,7 +5291,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5351,13 +5309,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5381,7 +5339,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5408,19 +5366,20 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5431,7 +5390,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5455,25 +5414,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9942
+          <t xml:space="preserve">1724
 </t>
         </is>
       </c>
@@ -5503,7 +5462,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
@@ -5515,7 +5474,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -5533,7 +5492,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5560,14 +5519,13 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5578,7 +5536,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5590,13 +5548,13 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5612,27 +5570,26 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4706
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -5641,7 +5598,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -5653,7 +5610,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5677,13 +5634,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5710,13 +5667,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -5728,61 +5685,61 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8180
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">9499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9506
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5794,13 +5751,13 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">12304
 </t>
         </is>
       </c>
@@ -5812,13 +5769,13 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5830,13 +5787,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36722
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5875,19 +5832,19 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25246
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5899,7 +5856,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -5908,25 +5865,24 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -5950,7 +5906,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5968,7 +5924,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5986,7 +5942,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -6019,31 +5975,31 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6055,19 +6011,19 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -6076,7 +6032,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">7960
 </t>
         </is>
       </c>
@@ -6094,7 +6050,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6106,19 +6062,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6130,7 +6086,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6172,7 +6128,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6184,7 +6140,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6196,13 +6152,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6220,7 +6176,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5118
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6238,25 +6194,25 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6274,13 +6230,13 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6313,34 +6269,34 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179 0
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">29
@@ -6349,7 +6305,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6361,13 +6317,13 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6376,15 +6332,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v/>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
@@ -6406,7 +6359,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6418,8 +6371,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6430,7 +6382,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -6469,25 +6421,25 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6499,7 +6451,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6511,21 +6463,18 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19502
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v/>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
@@ -6553,16 +6502,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 14
+</t>
+        </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6793,13 +6745,13 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6811,25 +6763,23 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>056</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
@@ -6841,13 +6791,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6874,37 +6823,37 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5097
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9663
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02712
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6949,7 +6898,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6967,22 +6916,25 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6994,7 +6946,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -7042,13 +6994,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111011
+          <t xml:space="preserve">872085
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -742,12 +742,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -771,13 +772,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>452</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -788,7 +790,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -822,15 +824,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v/>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -842,19 +841,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -866,33 +865,34 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -925,19 +925,19 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2439
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -955,7 +955,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -991,13 +991,13 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1045,19 +1045,19 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1081,13 +1081,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">3906
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2305
 </t>
         </is>
       </c>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1798
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1195,16 +1195,18 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1216,7 +1218,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1234,7 +1236,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1258,19 +1260,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1289,11 +1291,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v/>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -1309,8 +1308,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1327,7 +1325,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1360,13 +1358,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">7912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1390,7 +1388,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -1402,7 +1400,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1420,13 +1418,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1450,14 +1448,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">1479
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1468,14 +1465,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1486,37 +1482,38 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">39726
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t xml:space="preserve">4512
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1533,13 +1530,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -1569,18 +1566,20 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3826
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v/>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1597,11 +1596,8 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v/>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1611,7 +1607,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1623,13 +1619,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1641,13 +1637,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1665,19 +1661,20 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1700,7 +1697,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1730,13 +1727,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1760,7 +1757,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -1772,63 +1769,57 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v/>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v/>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>084</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1840,7 +1831,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1852,8 +1843,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1864,13 +1854,12 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -1886,8 +1875,11 @@
 </t>
         </is>
       </c>
-      <c r="Z11" s="3" t="n">
-        <v/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1904,11 +1896,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v/>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -1930,19 +1919,19 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">9 841
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1954,13 +1943,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1972,7 +1961,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1984,13 +1973,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2008,13 +1997,13 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2026,25 +2015,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -2074,7 +2063,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2086,7 +2075,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
@@ -2104,7 +2093,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2116,25 +2105,25 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2170,7 +2159,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -2194,13 +2183,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2219,8 +2208,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -2248,7 +2240,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2260,13 +2252,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2278,12 +2270,15 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2311,13 +2306,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -2347,7 +2342,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7172
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -2372,15 +2367,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v/>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2392,7 +2384,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2935
 </t>
         </is>
       </c>
@@ -2404,13 +2396,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">0179
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2422,8 +2414,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2440,19 +2431,19 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2470,7 +2461,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2488,7 +2479,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2512,7 +2503,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2536,54 +2527,51 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19404
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v/>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -2595,31 +2583,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532
+          <t xml:space="preserve">8532
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11273
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2631,39 +2619,44 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182
-</t>
+          <t>382</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100646
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9708
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -2685,25 +2678,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -2721,7 +2713,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2730,22 +2722,25 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -2757,7 +2752,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2769,25 +2764,25 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2805,12 +2800,15 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v/>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2832,49 +2830,45 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2889,24 +2883,27 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n">
-        <v/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0 2
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>892</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2923,13 +2920,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2947,18 +2944,20 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v/>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2977,13 +2976,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3007,12 +3006,13 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>469</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3036,12 +3036,15 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -3081,7 +3084,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3093,7 +3096,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3105,12 +3108,15 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v/>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -3127,18 +3133,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3150,7 +3159,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">0596
 </t>
         </is>
       </c>
@@ -3174,31 +3183,28 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v/>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
@@ -3222,13 +3228,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3240,7 +3246,7 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3252,7 +3258,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
@@ -3262,8 +3268,10 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="3" t="n">
-        <v/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -3280,12 +3288,16 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3296,7 +3308,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3308,7 +3320,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3326,7 +3338,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3359,13 +3371,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3377,39 +3389,45 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="n">
-        <v/>
-      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">903
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">08
 </t>
         </is>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v/>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3426,23 +3444,27 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3466,7 +3488,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3478,25 +3500,25 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">9912
 </t>
         </is>
       </c>
@@ -3508,13 +3530,13 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3526,7 +3548,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89562
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3538,30 +3560,33 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3583,7 +3608,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
@@ -3595,36 +3620,37 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3635,19 +3661,20 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">19529
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">9512
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -3661,54 +3688,57 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">377
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0949278
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">94256
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -3725,8 +3755,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -3760,42 +3793,48 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5812
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3807,19 +3846,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3831,7 +3870,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8217
 </t>
         </is>
       </c>
@@ -3841,8 +3880,11 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="3" t="n">
-        <v/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
@@ -3850,8 +3892,11 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n">
-        <v/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -3868,92 +3913,93 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3964,12 +4010,13 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -3981,19 +4028,18 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8713
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">693
 </t>
         </is>
       </c>
@@ -4015,18 +4061,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2986
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4038,7 +4087,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4062,28 +4111,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19896
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4101,13 +4153,13 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4125,30 +4177,33 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v/>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4188,7 +4243,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -4200,19 +4255,19 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4224,19 +4279,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">9222
 </t>
         </is>
       </c>
@@ -4248,13 +4303,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4272,33 +4327,39 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W27" s="3" t="n">
-        <v/>
-      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">802
 </t>
         </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v/>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -4320,13 +4381,13 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4338,7 +4399,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4362,60 +4423,61 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12724
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">402
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4427,29 +4489,33 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -4483,31 +4549,31 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4523,23 +4589,24 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v/>
+      <c r="M29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>407</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4557,7 +4624,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4575,30 +4642,33 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v/>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -4620,25 +4690,25 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">14984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4656,25 +4726,24 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
@@ -4683,7 +4752,8 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>453</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4700,7 +4770,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4724,29 +4794,32 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t xml:space="preserve">3122
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">524
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -4774,7 +4847,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4786,13 +4859,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4804,7 +4877,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4813,7 +4886,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4825,7 +4898,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -4843,25 +4916,25 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">641
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -4873,30 +4946,33 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7478
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -4913,24 +4989,26 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">12328
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4941,19 +5019,18 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4963,11 +5040,8 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
+      <c r="L32" s="3" t="n">
+        <v/>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -4975,25 +5049,27 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
-        <v/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -5010,7 +5086,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5022,7 +5098,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5034,12 +5110,14 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v/>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
       </c>
       <c r="Z32" s="3" t="n">
         <v/>
@@ -5059,12 +5137,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -5111,13 +5193,13 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5126,7 +5208,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5144,7 +5226,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5156,42 +5238,45 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v/>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -5219,13 +5304,13 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5237,7 +5322,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -5255,7 +5340,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5267,7 +5352,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5279,19 +5364,19 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5309,13 +5394,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5339,12 +5424,15 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -5361,8 +5449,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -5414,25 +5505,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1724
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5444,7 +5535,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5462,7 +5553,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -5496,8 +5587,11 @@
 </t>
         </is>
       </c>
-      <c r="Z35" s="3" t="n">
-        <v/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5519,13 +5613,14 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9336
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5554,7 +5649,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5566,27 +5661,31 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>707</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5598,7 +5697,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
@@ -5610,13 +5709,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -5634,7 +5733,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -5644,8 +5743,11 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n">
-        <v/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5673,7 +5775,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">19295
 </t>
         </is>
       </c>
@@ -5685,14 +5787,13 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5703,7 +5804,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5715,31 +5816,31 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">9511
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9502
+          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5751,43 +5852,43 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12304
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">73672
 </t>
         </is>
       </c>
@@ -5797,8 +5898,11 @@
 </t>
         </is>
       </c>
-      <c r="Z37" s="3" t="n">
-        <v/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2473
+</t>
+        </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -5832,7 +5936,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5856,7 +5960,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -5865,24 +5969,25 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
@@ -5900,54 +6005,57 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">7235
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">149
 </t>
         </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v/>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -5969,37 +6077,35 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6011,19 +6117,19 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6032,7 +6138,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
@@ -6050,51 +6156,56 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v/>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -6111,8 +6222,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -6128,7 +6242,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -6140,7 +6254,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6152,13 +6266,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6170,13 +6284,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6194,13 +6308,13 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6212,22 +6326,22 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -6236,7 +6350,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6246,8 +6360,11 @@
 </t>
         </is>
       </c>
-      <c r="Z40" s="3" t="n">
-        <v/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8262
+</t>
+        </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -6269,13 +6386,13 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179 0
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6293,14 +6410,13 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6311,13 +6427,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2091
 </t>
         </is>
       </c>
@@ -6332,16 +6448,19 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6359,30 +6478,31 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6392,8 +6512,11 @@
 </t>
         </is>
       </c>
-      <c r="Z41" s="3" t="n">
-        <v/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6413,33 +6536,30 @@
       <c r="C42" s="3" t="n">
         <v/>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">324
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6451,78 +6571,87 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">86
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 14
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="X42" s="3" t="n">
         <v/>
@@ -6745,58 +6874,57 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>056</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v/>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">23662
 </t>
         </is>
       </c>
@@ -6806,12 +6934,15 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n">
-        <v/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
@@ -6823,19 +6954,19 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8927
 </t>
         </is>
       </c>
@@ -6847,18 +6978,21 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
+          <t xml:space="preserve">193272
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6880,28 +7014,28 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -6910,37 +7044,37 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6952,60 +7086,66 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v/>
-      </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n">
-        <v/>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">602
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872085
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+      <c r="Y46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 9929
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -682,122 +682,102 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="n">
@@ -829,140 +809,117 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -985,140 +942,117 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1141,62 +1075,52 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1206,74 +1130,62 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1296,14 +1208,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1313,44 +1223,37 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
@@ -1358,74 +1261,62 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1448,8 +1339,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1459,14 +1349,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1476,92 +1364,77 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39726
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>488</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1571,14 +1444,12 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
-</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1601,140 +1472,117 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1757,26 +1605,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
@@ -1784,8 +1628,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
@@ -1801,44 +1644,37 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1848,8 +1684,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1859,26 +1694,22 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1901,140 +1732,117 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 841
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2057,140 +1865,117 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2210,146 +1995,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2372,44 +2133,37 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2935
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2419,92 +2173,77 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2527,20 +2266,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2550,20 +2286,17 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
@@ -2571,50 +2304,42 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2624,38 +2349,32 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9708
-</t>
+          <t>088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2673,19 +2392,19 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2695,26 +2414,22 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2722,92 +2437,77 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2850,20 +2550,17 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2873,32 +2570,27 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 2
-</t>
+          <t>0 2</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2908,38 +2600,32 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
-</t>
+          <t>542</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2949,14 +2635,12 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2976,146 +2660,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3135,68 +2795,57 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0596
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
@@ -3204,68 +2853,57 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3290,143 +2928,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v/>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3446,146 +3063,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3608,20 +3201,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3631,50 +3221,42 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19529
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9512
-</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -3682,62 +3264,52 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
-</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
-</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94256
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3757,44 +3329,37 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3804,98 +3369,82 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
+          <t>99919991</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3918,20 +3467,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3941,14 +3487,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3958,38 +3502,32 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -4004,26 +3542,22 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4033,14 +3567,12 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">693
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n">
@@ -4063,146 +3595,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19896
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4225,140 +3733,117 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4381,140 +3866,117 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>402</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4537,56 +3999,47 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
@@ -4594,80 +4047,67 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4690,44 +4130,37 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14984
-</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4737,14 +4170,12 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3921
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
@@ -4752,68 +4183,57 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3122
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4841,44 +4261,37 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4886,92 +4299,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7478
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4991,14 +4389,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12328
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5013,14 +4409,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -5030,14 +4424,12 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
@@ -5045,26 +4437,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5074,38 +4462,32 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
@@ -5115,8 +4497,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n">
@@ -5139,68 +4520,57 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
@@ -5208,74 +4578,62 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5293,145 +4651,124 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5451,146 +4788,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5613,140 +4926,117 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9336
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5769,26 +5059,22 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19295
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5798,110 +5084,92 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9499
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9511
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1502
-</t>
+          <t>502</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
-</t>
+          <t>703</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73672
-</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5924,137 +5192,117 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6077,8 +5325,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6088,8 +5335,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -6099,38 +5345,32 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
@@ -6138,56 +5378,47 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241 7</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -6197,14 +5428,12 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6224,146 +5453,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
+          <t>472</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8262
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6386,32 +5591,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -6421,26 +5621,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
@@ -6448,74 +5644,62 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6541,116 +5725,97 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="X42" s="3" t="n">
@@ -6679,8 +5844,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -6769,8 +5933,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -6862,26 +6025,22 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6891,32 +6050,27 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
@@ -6924,74 +6078,62 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23662
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2412
-</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
-</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8927
-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193272
-</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7014,128 +6156,107 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n">
@@ -7143,8 +6264,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 9929
-</t>
+          <t>0 22</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2 81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>742</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>173</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>412</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>347</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>99919991</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>856</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>293</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>000</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>278</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>921</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>451</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4208,17 +4208,17 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>876</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>903</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>286</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>254</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>241 7</t>
+          <t>241 0</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5770,52 +5770,52 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X42" s="3" t="n">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>963</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6206,42 +6206,42 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -6259,12 +6259,14 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>0 22</t>
+          <t>00 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/508/508_198802_SF.JPG_pre_QA_QC.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>905</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>67</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0 1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>919</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>109</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>114</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2419,57 +2419,57 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
           <t>253</t>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2705,22 +2705,22 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>193</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0 01</t>
+          <t>0 0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>88</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>577</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>812</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n">
@@ -3595,67 +3595,67 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>08</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>63</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4218,17 +4218,17 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>803</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4603,17 +4603,17 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>290</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>09</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4971,17 +4971,17 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>155</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5227,37 +5227,37 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>886</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5503,17 +5503,17 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>869</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5606,90 +5606,90 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t>828</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>241</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6108,22 +6108,22 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6181,42 +6181,42 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6259,14 +6259,12 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>2 1</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v/>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>00 2989</t>
+          <t>0 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
